--- a/cases/AConly_psse_3W_unigrid_easy.xlsx
+++ b/cases/AConly_psse_3W_unigrid_easy.xlsx
@@ -4953,7 +4953,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>900000000</v>
+        <v>900</v>
       </c>
       <c r="K2" t="n">
         <v>1e-06</v>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>950000000</v>
+        <v>950</v>
       </c>
       <c r="K3" t="n">
         <v>1e-06</v>
@@ -5047,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1000000000</v>
+        <v>1000</v>
       </c>
       <c r="K4" t="n">
         <v>1e-06</v>
@@ -5094,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>725000000</v>
+        <v>725</v>
       </c>
       <c r="K5" t="n">
         <v>1e-06</v>
@@ -5141,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1050000000</v>
+        <v>1050</v>
       </c>
       <c r="K6" t="n">
         <v>1e-06</v>
@@ -5188,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>530000000</v>
+        <v>530</v>
       </c>
       <c r="K7" t="n">
         <v>1e-06</v>
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>120000000</v>
+        <v>120</v>
       </c>
       <c r="K8" t="n">
         <v>1e-06</v>
